--- a/estonian_vocabulary.xlsx
+++ b/estonian_vocabulary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VasilikiBalidou\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC99D9B-8AC5-4DD9-9885-B82D8C686146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4013F4C3-79E8-4A80-B58A-1092800B8F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="1871">
   <si>
     <t>Chapter</t>
   </si>
@@ -2620,9 +2620,6 @@
     <t>chess</t>
   </si>
   <si>
-    <t>Sports</t>
-  </si>
-  <si>
     <t>football</t>
   </si>
   <si>
@@ -3055,12 +3052,6 @@
     <t>amusement park</t>
   </si>
   <si>
-    <t>Buildings</t>
-  </si>
-  <si>
-    <t>metro</t>
-  </si>
-  <si>
     <t>kindergarten</t>
   </si>
   <si>
@@ -3502,9 +3493,6 @@
     <t>block</t>
   </si>
   <si>
-    <t>vegetables</t>
-  </si>
-  <si>
     <t>movement verbs</t>
   </si>
   <si>
@@ -3559,26 +3547,2117 @@
     <t>terraced house</t>
   </si>
   <si>
-    <t>bugs</t>
-  </si>
-  <si>
-    <t>fruits</t>
-  </si>
-  <si>
-    <t>nuts</t>
-  </si>
-  <si>
     <t>trikoo</t>
   </si>
   <si>
-    <t>vehicles</t>
+    <t>õun</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>pirn</t>
+  </si>
+  <si>
+    <t>pear</t>
+  </si>
+  <si>
+    <t>banaan</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>viinamarjad</t>
+  </si>
+  <si>
+    <t>grapes</t>
+  </si>
+  <si>
+    <t>sidrun</t>
+  </si>
+  <si>
+    <t>lemon</t>
+  </si>
+  <si>
+    <t>apelsin</t>
+  </si>
+  <si>
+    <t>mandariin</t>
+  </si>
+  <si>
+    <t>greip</t>
+  </si>
+  <si>
+    <t>grapefruit</t>
+  </si>
+  <si>
+    <t>laim</t>
+  </si>
+  <si>
+    <t>lime</t>
+  </si>
+  <si>
+    <t>arbuus</t>
+  </si>
+  <si>
+    <t>watermelon</t>
+  </si>
+  <si>
+    <t>melon</t>
+  </si>
+  <si>
+    <t>ananass</t>
+  </si>
+  <si>
+    <t>pineapple</t>
+  </si>
+  <si>
+    <t>kiivi</t>
+  </si>
+  <si>
+    <t>kiwi</t>
+  </si>
+  <si>
+    <t>granaatõun</t>
+  </si>
+  <si>
+    <t>pomegranate</t>
+  </si>
+  <si>
+    <t>kirss</t>
+  </si>
+  <si>
+    <t>cherry</t>
+  </si>
+  <si>
+    <t>murel</t>
+  </si>
+  <si>
+    <t>sweet cherry</t>
+  </si>
+  <si>
+    <t>ploom</t>
+  </si>
+  <si>
+    <t>plum</t>
+  </si>
+  <si>
+    <t>virsik</t>
+  </si>
+  <si>
+    <t>peach</t>
+  </si>
+  <si>
+    <t>aprikoos</t>
+  </si>
+  <si>
+    <t>apricot</t>
+  </si>
+  <si>
+    <t>maasikas</t>
+  </si>
+  <si>
+    <t>strawberry</t>
+  </si>
+  <si>
+    <t>metsmaasikas</t>
+  </si>
+  <si>
+    <t>wild strawberry</t>
+  </si>
+  <si>
+    <t>vaarikas</t>
+  </si>
+  <si>
+    <t>raspberry</t>
+  </si>
+  <si>
+    <t>mustikas</t>
+  </si>
+  <si>
+    <t>jõhvikas</t>
+  </si>
+  <si>
+    <t>cranberry</t>
+  </si>
+  <si>
+    <t>põldmari</t>
+  </si>
+  <si>
+    <t>blackberry</t>
+  </si>
+  <si>
+    <t>avokaado</t>
+  </si>
+  <si>
+    <t>avocado</t>
+  </si>
+  <si>
+    <t>puuvili</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>marjad</t>
+  </si>
+  <si>
+    <t>berries</t>
+  </si>
+  <si>
+    <t>mandarin</t>
+  </si>
+  <si>
+    <t>blueberry</t>
+  </si>
+  <si>
+    <t>kartul</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>porgand</t>
+  </si>
+  <si>
+    <t>carrot</t>
+  </si>
+  <si>
+    <t>kapsas</t>
+  </si>
+  <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>lillkapsas</t>
+  </si>
+  <si>
+    <t>cauliflower</t>
+  </si>
+  <si>
+    <t>brokoli</t>
+  </si>
+  <si>
+    <t>broccoli</t>
+  </si>
+  <si>
+    <t>peet</t>
+  </si>
+  <si>
+    <t>redis</t>
+  </si>
+  <si>
+    <t>radish</t>
+  </si>
+  <si>
+    <t>kõrvits</t>
+  </si>
+  <si>
+    <t>pumpkin</t>
+  </si>
+  <si>
+    <t>kurk</t>
+  </si>
+  <si>
+    <t>cucumber</t>
+  </si>
+  <si>
+    <t>tomat</t>
+  </si>
+  <si>
+    <t>tomato</t>
+  </si>
+  <si>
+    <t>paprika</t>
+  </si>
+  <si>
+    <t>bell pepper / sweet pepper</t>
+  </si>
+  <si>
+    <t>hernes</t>
+  </si>
+  <si>
+    <t>uba</t>
+  </si>
+  <si>
+    <t>bean</t>
+  </si>
+  <si>
+    <t>sibul</t>
+  </si>
+  <si>
+    <t>onion</t>
+  </si>
+  <si>
+    <t>küüslauk</t>
+  </si>
+  <si>
+    <t>garlic</t>
+  </si>
+  <si>
+    <t>petersell</t>
+  </si>
+  <si>
+    <t>parsley</t>
+  </si>
+  <si>
+    <t>till</t>
+  </si>
+  <si>
+    <t>dill</t>
+  </si>
+  <si>
+    <t>spinat</t>
+  </si>
+  <si>
+    <t>spinach</t>
+  </si>
+  <si>
+    <t>oliivid</t>
+  </si>
+  <si>
+    <t>olives</t>
+  </si>
+  <si>
+    <t>mais</t>
+  </si>
+  <si>
+    <t>köögivili</t>
+  </si>
+  <si>
+    <t>vegetable</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>beetroot</t>
+  </si>
+  <si>
+    <t>corn</t>
+  </si>
+  <si>
+    <t>mandel</t>
+  </si>
+  <si>
+    <t>almond</t>
+  </si>
+  <si>
+    <t>walnut</t>
+  </si>
+  <si>
+    <t>sarapuupähkel</t>
+  </si>
+  <si>
+    <t>hazelnut</t>
+  </si>
+  <si>
+    <t>maapähkel</t>
+  </si>
+  <si>
+    <t>peanut</t>
+  </si>
+  <si>
+    <t>pekanipähkel</t>
+  </si>
+  <si>
+    <t>pecan</t>
+  </si>
+  <si>
+    <t>cashew</t>
+  </si>
+  <si>
+    <t>pistaatsiapähkel</t>
+  </si>
+  <si>
+    <t>pistachio</t>
+  </si>
+  <si>
+    <t>kookos</t>
+  </si>
+  <si>
+    <t>coconut</t>
+  </si>
+  <si>
+    <t>päevalilleseemned</t>
+  </si>
+  <si>
+    <t>sunflower seeds</t>
+  </si>
+  <si>
+    <t>kõrvitsaseemned</t>
+  </si>
+  <si>
+    <t>pumpkin seeds</t>
+  </si>
+  <si>
+    <t>kreeka pähkel</t>
+  </si>
+  <si>
+    <t>india pähkel</t>
+  </si>
+  <si>
+    <t>pähkel</t>
+  </si>
+  <si>
+    <t>nut</t>
+  </si>
+  <si>
+    <t>seemned</t>
+  </si>
+  <si>
+    <t>seeds</t>
+  </si>
+  <si>
+    <t>leib</t>
+  </si>
+  <si>
+    <t>sai</t>
+  </si>
+  <si>
+    <t>white bread</t>
+  </si>
+  <si>
+    <t>puder</t>
+  </si>
+  <si>
+    <t>porridge</t>
+  </si>
+  <si>
+    <t>muna</t>
+  </si>
+  <si>
+    <t>egg</t>
+  </si>
+  <si>
+    <t>juust</t>
+  </si>
+  <si>
+    <t>cheese</t>
+  </si>
+  <si>
+    <t>vorst</t>
+  </si>
+  <si>
+    <t>sausage</t>
+  </si>
+  <si>
+    <t>ham</t>
+  </si>
+  <si>
+    <t>kaerahelbed</t>
+  </si>
+  <si>
+    <t>riis</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>jahu</t>
+  </si>
+  <si>
+    <t>flour</t>
+  </si>
+  <si>
+    <t>keedukartul</t>
+  </si>
+  <si>
+    <t>boiled potato</t>
+  </si>
+  <si>
+    <t>praekartul</t>
+  </si>
+  <si>
+    <t>fried potato</t>
+  </si>
+  <si>
+    <t>ahjukartul</t>
+  </si>
+  <si>
+    <t>kartulipuder</t>
+  </si>
+  <si>
+    <t>mashed potatoes</t>
+  </si>
+  <si>
+    <t>salat</t>
+  </si>
+  <si>
+    <t>salad</t>
+  </si>
+  <si>
+    <t>kaste</t>
+  </si>
+  <si>
+    <t>sauce / gravy</t>
+  </si>
+  <si>
+    <t>kala</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>kana</t>
+  </si>
+  <si>
+    <t>chicken</t>
+  </si>
+  <si>
+    <t>liha</t>
+  </si>
+  <si>
+    <t>meat</t>
+  </si>
+  <si>
+    <t>hakkliha</t>
+  </si>
+  <si>
+    <t>supp</t>
+  </si>
+  <si>
+    <t>soup</t>
+  </si>
+  <si>
+    <t>pirukas</t>
+  </si>
+  <si>
+    <t>friikartulid</t>
+  </si>
+  <si>
+    <t>krõpsud</t>
+  </si>
+  <si>
+    <t>crisps / chips</t>
+  </si>
+  <si>
+    <t>sool</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>pipar</t>
+  </si>
+  <si>
+    <t>pepper</t>
+  </si>
+  <si>
+    <t>suhkur</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>või</t>
+  </si>
+  <si>
+    <t>butter</t>
+  </si>
+  <si>
+    <t>õli</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>oats</t>
+  </si>
+  <si>
+    <t>roasted potato</t>
+  </si>
+  <si>
+    <t>minced meat</t>
+  </si>
+  <si>
+    <t>french fries</t>
+  </si>
+  <si>
+    <t>rye bread</t>
+  </si>
+  <si>
+    <t>toit</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>magustoit</t>
+  </si>
+  <si>
+    <t>dessert / sweet</t>
+  </si>
+  <si>
+    <t>tort</t>
+  </si>
+  <si>
+    <t>cake / celebration cake</t>
+  </si>
+  <si>
+    <t>kook</t>
+  </si>
+  <si>
+    <t>cake</t>
+  </si>
+  <si>
+    <t>pannkoogid</t>
+  </si>
+  <si>
+    <t>pancakes</t>
+  </si>
+  <si>
+    <t>šokolaad</t>
+  </si>
+  <si>
+    <t>chocolate</t>
+  </si>
+  <si>
+    <t>komm</t>
+  </si>
+  <si>
+    <t>sweet / candy</t>
+  </si>
+  <si>
+    <t>pulgakomm</t>
+  </si>
+  <si>
+    <t>lollipop</t>
+  </si>
+  <si>
+    <t>küpsis</t>
+  </si>
+  <si>
+    <t>biscuit / cookie</t>
+  </si>
+  <si>
+    <t>vahvel</t>
+  </si>
+  <si>
+    <t>wafer</t>
+  </si>
+  <si>
+    <t>jäätis</t>
+  </si>
+  <si>
+    <t>ice cream</t>
+  </si>
+  <si>
+    <t>moos</t>
+  </si>
+  <si>
+    <t>jam</t>
+  </si>
+  <si>
+    <t>mesi</t>
+  </si>
+  <si>
+    <t>honey</t>
+  </si>
+  <si>
+    <t>rosin</t>
+  </si>
+  <si>
+    <t>raisin</t>
+  </si>
+  <si>
+    <t>dattel</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>piparkook</t>
+  </si>
+  <si>
+    <t>gingerbread cookie</t>
+  </si>
+  <si>
+    <t>jook</t>
+  </si>
+  <si>
+    <t>drink</t>
+  </si>
+  <si>
+    <t>vesi</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>piim</t>
+  </si>
+  <si>
+    <t>milk</t>
+  </si>
+  <si>
+    <t>tee</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>kohv</t>
+  </si>
+  <si>
+    <t>coffee</t>
+  </si>
+  <si>
+    <t>kohvikoor</t>
+  </si>
+  <si>
+    <t>coffee cream</t>
+  </si>
+  <si>
+    <t>mahl</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>limonaad</t>
+  </si>
+  <si>
+    <t>šampanja</t>
+  </si>
+  <si>
+    <t>champagne</t>
+  </si>
+  <si>
+    <t>vein</t>
+  </si>
+  <si>
+    <t>wine</t>
+  </si>
+  <si>
+    <t>õlu</t>
+  </si>
+  <si>
+    <t>beer</t>
+  </si>
+  <si>
+    <t>kokteil</t>
+  </si>
+  <si>
+    <t>cocktail</t>
+  </si>
+  <si>
+    <t>lemonade</t>
+  </si>
+  <si>
+    <t>pie</t>
+  </si>
+  <si>
+    <t>saiake</t>
+  </si>
+  <si>
+    <t>pastry</t>
+  </si>
+  <si>
+    <t>kastan</t>
+  </si>
+  <si>
+    <t>chestnut</t>
+  </si>
+  <si>
+    <t>suvikõrvits</t>
+  </si>
+  <si>
+    <t>zucchini</t>
+  </si>
+  <si>
+    <t>baklažaan</t>
+  </si>
+  <si>
+    <t>eggplant / aubergine</t>
+  </si>
+  <si>
+    <t>seened</t>
+  </si>
+  <si>
+    <t>mushrooms</t>
+  </si>
+  <si>
+    <t>sõiduk</t>
+  </si>
+  <si>
+    <t>vehicle</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>car</t>
+  </si>
+  <si>
+    <t>buss</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>tramm</t>
+  </si>
+  <si>
+    <t>tram</t>
+  </si>
+  <si>
+    <t>troll</t>
+  </si>
+  <si>
+    <t>takso</t>
+  </si>
+  <si>
+    <t>taxi</t>
+  </si>
+  <si>
+    <t>rong</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>jalgratas</t>
+  </si>
+  <si>
+    <t>bicycle / bike</t>
+  </si>
+  <si>
+    <t>tõukeratas</t>
+  </si>
+  <si>
+    <t>mootorratas</t>
+  </si>
+  <si>
+    <t>motorcycle</t>
+  </si>
+  <si>
+    <t>mopeed</t>
+  </si>
+  <si>
+    <t>moped</t>
+  </si>
+  <si>
+    <t>traktor</t>
+  </si>
+  <si>
+    <t>tractor</t>
+  </si>
+  <si>
+    <t>laev</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>praam</t>
+  </si>
+  <si>
+    <t>ferry</t>
+  </si>
+  <si>
+    <t>jaht</t>
+  </si>
+  <si>
+    <t>yacht</t>
+  </si>
+  <si>
+    <t>kaater</t>
+  </si>
+  <si>
+    <t>motorboat / speedboat</t>
+  </si>
+  <si>
+    <t>paat</t>
+  </si>
+  <si>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>lennuk</t>
+  </si>
+  <si>
+    <t>airplane / plane</t>
+  </si>
+  <si>
+    <t>helikopter</t>
+  </si>
+  <si>
+    <t>helicopter</t>
+  </si>
+  <si>
+    <t>trolley</t>
+  </si>
+  <si>
+    <t>scooter</t>
+  </si>
+  <si>
+    <t>kiirabi</t>
+  </si>
+  <si>
+    <t>ambulance</t>
+  </si>
+  <si>
+    <t>tuletõrjeauto</t>
+  </si>
+  <si>
+    <t>fire truck</t>
+  </si>
+  <si>
+    <t>matkaauto</t>
+  </si>
+  <si>
+    <t>camper van</t>
+  </si>
+  <si>
+    <t>lumesahk</t>
+  </si>
+  <si>
+    <t>snowplow</t>
+  </si>
+  <si>
+    <t>subway</t>
+  </si>
+  <si>
+    <t>kuumaõhupall</t>
+  </si>
+  <si>
+    <t>hot air balloon</t>
+  </si>
+  <si>
+    <t>langevari</t>
+  </si>
+  <si>
+    <t>parachute</t>
+  </si>
+  <si>
+    <t>allveelaev</t>
+  </si>
+  <si>
+    <t>submarine</t>
+  </si>
+  <si>
+    <t>kruiisilaev</t>
+  </si>
+  <si>
+    <t>cruise ship</t>
+  </si>
+  <si>
+    <t>Buildings &amp; Vehicles</t>
+  </si>
+  <si>
+    <t>roos</t>
+  </si>
+  <si>
+    <t>rose</t>
+  </si>
+  <si>
+    <t>päevalill</t>
+  </si>
+  <si>
+    <t>sunflower</t>
+  </si>
+  <si>
+    <t>vesiroos</t>
+  </si>
+  <si>
+    <t>water lily</t>
+  </si>
+  <si>
+    <t>lind</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>kukk</t>
+  </si>
+  <si>
+    <t>rooster / cock</t>
+  </si>
+  <si>
+    <t>kalkun</t>
+  </si>
+  <si>
+    <t>turkey</t>
+  </si>
+  <si>
+    <t>hani</t>
+  </si>
+  <si>
+    <t>goose</t>
+  </si>
+  <si>
+    <t>luik</t>
+  </si>
+  <si>
+    <t>swan</t>
+  </si>
+  <si>
+    <t>part</t>
+  </si>
+  <si>
+    <t>duck</t>
+  </si>
+  <si>
+    <t>kajakas</t>
+  </si>
+  <si>
+    <t>varblane</t>
+  </si>
+  <si>
+    <t>sparrow</t>
+  </si>
+  <si>
+    <t>pääsuke</t>
+  </si>
+  <si>
+    <t>swallow</t>
+  </si>
+  <si>
+    <t>tuvi</t>
+  </si>
+  <si>
+    <t>pigeon / dove</t>
+  </si>
+  <si>
+    <t>vares</t>
+  </si>
+  <si>
+    <t>crow</t>
+  </si>
+  <si>
+    <t>kotkas</t>
+  </si>
+  <si>
+    <t>eagle</t>
+  </si>
+  <si>
+    <t>öökull</t>
+  </si>
+  <si>
+    <t>owl</t>
+  </si>
+  <si>
+    <t>paabulind</t>
+  </si>
+  <si>
+    <t>peacock</t>
+  </si>
+  <si>
+    <t>papagoi</t>
+  </si>
+  <si>
+    <t>parrot</t>
+  </si>
+  <si>
+    <t>pingviin</t>
+  </si>
+  <si>
+    <t>penguin</t>
+  </si>
+  <si>
+    <t>seagull</t>
+  </si>
+  <si>
+    <t>loom</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>koduloom</t>
+  </si>
+  <si>
+    <t>pet</t>
+  </si>
+  <si>
+    <t>metsloom</t>
+  </si>
+  <si>
+    <t>wild animal</t>
+  </si>
+  <si>
+    <t>kass</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>koer</t>
+  </si>
+  <si>
+    <t>dog</t>
+  </si>
+  <si>
+    <t>hiir</t>
+  </si>
+  <si>
+    <t>merisiga</t>
+  </si>
+  <si>
+    <t>guinea pig</t>
+  </si>
+  <si>
+    <t>rott</t>
+  </si>
+  <si>
+    <t>rat</t>
+  </si>
+  <si>
+    <t>hobune</t>
+  </si>
+  <si>
+    <t>horse</t>
+  </si>
+  <si>
+    <t>eesel</t>
+  </si>
+  <si>
+    <t>donkey</t>
+  </si>
+  <si>
+    <t>lehm</t>
+  </si>
+  <si>
+    <t>cow</t>
+  </si>
+  <si>
+    <t>siga</t>
+  </si>
+  <si>
+    <t>pig</t>
+  </si>
+  <si>
+    <t>lammas</t>
+  </si>
+  <si>
+    <t>sheep</t>
+  </si>
+  <si>
+    <t>kits</t>
+  </si>
+  <si>
+    <t>goat</t>
+  </si>
+  <si>
+    <t>küülik</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+  </si>
+  <si>
+    <t>põder</t>
+  </si>
+  <si>
+    <t>hirv</t>
+  </si>
+  <si>
+    <t>deer</t>
+  </si>
+  <si>
+    <t>karu</t>
+  </si>
+  <si>
+    <t>bear</t>
+  </si>
+  <si>
+    <t>hunt</t>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>rebane</t>
+  </si>
+  <si>
+    <t>fox</t>
+  </si>
+  <si>
+    <t>metssiga</t>
+  </si>
+  <si>
+    <t>wild boar</t>
+  </si>
+  <si>
+    <t>jänes</t>
+  </si>
+  <si>
+    <t>hare</t>
+  </si>
+  <si>
+    <t>orav</t>
+  </si>
+  <si>
+    <t>squirrel</t>
+  </si>
+  <si>
+    <t>siil</t>
+  </si>
+  <si>
+    <t>hedgehog</t>
+  </si>
+  <si>
+    <t>konn</t>
+  </si>
+  <si>
+    <t>frog</t>
+  </si>
+  <si>
+    <t>tigu</t>
+  </si>
+  <si>
+    <t>snail</t>
+  </si>
+  <si>
+    <t>elevant</t>
+  </si>
+  <si>
+    <t>elephant</t>
+  </si>
+  <si>
+    <t>kaelkirjak</t>
+  </si>
+  <si>
+    <t>giraffe</t>
+  </si>
+  <si>
+    <t>ninasarvik</t>
+  </si>
+  <si>
+    <t>jõehobu</t>
+  </si>
+  <si>
+    <t>lõvi</t>
+  </si>
+  <si>
+    <t>lion</t>
+  </si>
+  <si>
+    <t>tiiger</t>
+  </si>
+  <si>
+    <t>tiger</t>
+  </si>
+  <si>
+    <t>ahv</t>
+  </si>
+  <si>
+    <t>monkey</t>
+  </si>
+  <si>
+    <t>krokodill</t>
+  </si>
+  <si>
+    <t>crocodile</t>
+  </si>
+  <si>
+    <t>kilpkonn</t>
+  </si>
+  <si>
+    <t>turtle / tortoise</t>
+  </si>
+  <si>
+    <t>madu</t>
+  </si>
+  <si>
+    <t>snake</t>
+  </si>
+  <si>
+    <t>delfiin</t>
+  </si>
+  <si>
+    <t>dolphin</t>
+  </si>
+  <si>
+    <t>vaal</t>
+  </si>
+  <si>
+    <t>whale</t>
+  </si>
+  <si>
+    <t>jääkaru</t>
+  </si>
+  <si>
+    <t>polar bear</t>
+  </si>
+  <si>
+    <t>hüljes</t>
+  </si>
+  <si>
+    <t>seal</t>
+  </si>
+  <si>
+    <t>pull</t>
+  </si>
+  <si>
+    <t>bull</t>
+  </si>
+  <si>
+    <t>põrsas</t>
+  </si>
+  <si>
+    <t>piglet</t>
+  </si>
+  <si>
+    <t>putukas</t>
+  </si>
+  <si>
+    <t>insect</t>
+  </si>
+  <si>
+    <t>kärbes</t>
+  </si>
+  <si>
+    <t>fly</t>
+  </si>
+  <si>
+    <t>sääsk</t>
+  </si>
+  <si>
+    <t>mosquito</t>
+  </si>
+  <si>
+    <t>herilane</t>
+  </si>
+  <si>
+    <t>wasp</t>
+  </si>
+  <si>
+    <t>mesilane</t>
+  </si>
+  <si>
+    <t>bee</t>
+  </si>
+  <si>
+    <t>liblikas</t>
+  </si>
+  <si>
+    <t>butterfly</t>
+  </si>
+  <si>
+    <t>lepatriinu</t>
+  </si>
+  <si>
+    <t>ladybird / ladybug</t>
+  </si>
+  <si>
+    <t>mardikas</t>
+  </si>
+  <si>
+    <t>beetle</t>
+  </si>
+  <si>
+    <t>sipelgas</t>
+  </si>
+  <si>
+    <t>ant</t>
+  </si>
+  <si>
+    <t>rohutirts</t>
+  </si>
+  <si>
+    <t>grasshopper</t>
+  </si>
+  <si>
+    <t>prussakas</t>
+  </si>
+  <si>
+    <t>cockroach</t>
+  </si>
+  <si>
+    <t>ämblik</t>
+  </si>
+  <si>
+    <t>spider</t>
+  </si>
+  <si>
+    <t>täi</t>
+  </si>
+  <si>
+    <t>louse</t>
+  </si>
+  <si>
+    <t>kirp</t>
+  </si>
+  <si>
+    <t>flea</t>
+  </si>
+  <si>
+    <t>puuk</t>
+  </si>
+  <si>
+    <t>tick</t>
+  </si>
+  <si>
+    <t>sajajalgne</t>
+  </si>
+  <si>
+    <t>centipede</t>
+  </si>
+  <si>
+    <t>uss</t>
+  </si>
+  <si>
+    <t>worm</t>
+  </si>
+  <si>
+    <t>nahkhiir</t>
+  </si>
+  <si>
+    <t>bat</t>
+  </si>
+  <si>
+    <t>nälkjas</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>sisalik</t>
+  </si>
+  <si>
+    <t>lizard</t>
+  </si>
+  <si>
+    <t>põhjapõder</t>
+  </si>
+  <si>
+    <t>reindeer</t>
+  </si>
+  <si>
+    <t>moose</t>
+  </si>
+  <si>
+    <t>hüään</t>
+  </si>
+  <si>
+    <t>hyena</t>
+  </si>
+  <si>
+    <t>rhino / rhinoceros</t>
+  </si>
+  <si>
+    <t>hippo</t>
+  </si>
+  <si>
+    <t>merihobu</t>
+  </si>
+  <si>
+    <t>seahorse</t>
+  </si>
+  <si>
+    <t>merisiilik</t>
+  </si>
+  <si>
+    <t>sea urchin</t>
+  </si>
+  <si>
+    <t>meritäht</t>
+  </si>
+  <si>
+    <t>starfish</t>
+  </si>
+  <si>
+    <t>krabi</t>
+  </si>
+  <si>
+    <t>crab</t>
+  </si>
+  <si>
+    <t>homaar</t>
+  </si>
+  <si>
+    <t>lobster</t>
+  </si>
+  <si>
+    <t>kaheksajalg</t>
+  </si>
+  <si>
+    <t>octopus</t>
+  </si>
+  <si>
+    <t>meduus</t>
+  </si>
+  <si>
+    <t>jellyfish</t>
+  </si>
+  <si>
+    <t>hai</t>
+  </si>
+  <si>
+    <t>shark</t>
+  </si>
+  <si>
+    <t>kalmaar</t>
+  </si>
+  <si>
+    <t>squid</t>
+  </si>
+  <si>
+    <t>kaaren</t>
+  </si>
+  <si>
+    <t>raven</t>
+  </si>
+  <si>
+    <t>raisakotkas</t>
+  </si>
+  <si>
+    <t>vulture</t>
+  </si>
+  <si>
+    <t>lõhe</t>
+  </si>
+  <si>
+    <t>salmon</t>
+  </si>
+  <si>
+    <t>angerjas</t>
+  </si>
+  <si>
+    <t>eel</t>
+  </si>
+  <si>
+    <t>mets</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>mägi</t>
+  </si>
+  <si>
+    <t>mountain</t>
+  </si>
+  <si>
+    <t>meri</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>ookean</t>
+  </si>
+  <si>
+    <t>ocean</t>
+  </si>
+  <si>
+    <t>jõgi</t>
+  </si>
+  <si>
+    <t>river</t>
+  </si>
+  <si>
+    <t>oja</t>
+  </si>
+  <si>
+    <t>stream / creek</t>
+  </si>
+  <si>
+    <t>järv</t>
+  </si>
+  <si>
+    <t>lake</t>
+  </si>
+  <si>
+    <t>tiik</t>
+  </si>
+  <si>
+    <t>pond</t>
+  </si>
+  <si>
+    <t>raba</t>
+  </si>
+  <si>
+    <t>bog</t>
+  </si>
+  <si>
+    <t>soo</t>
+  </si>
+  <si>
+    <t>põld</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>rand</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>kõrb</t>
+  </si>
+  <si>
+    <t>desert</t>
+  </si>
+  <si>
+    <t>moon</t>
+  </si>
+  <si>
+    <t>loodus</t>
+  </si>
+  <si>
+    <t>nature</t>
+  </si>
+  <si>
+    <t>kuusk</t>
+  </si>
+  <si>
+    <t>spruce tree</t>
+  </si>
+  <si>
+    <t>kosk</t>
+  </si>
+  <si>
+    <t>waterfall</t>
+  </si>
+  <si>
+    <t>saar</t>
+  </si>
+  <si>
+    <t>island</t>
+  </si>
+  <si>
+    <t>maailm</t>
+  </si>
+  <si>
+    <t>world</t>
+  </si>
+  <si>
+    <t>adru</t>
+  </si>
+  <si>
+    <t>seaweed</t>
+  </si>
+  <si>
+    <t>koobas</t>
+  </si>
+  <si>
+    <t>cave</t>
+  </si>
+  <si>
+    <t>vulkaan</t>
+  </si>
+  <si>
+    <t>volcano</t>
+  </si>
+  <si>
+    <t>põhjapoolus</t>
+  </si>
+  <si>
+    <t>north pole</t>
+  </si>
+  <si>
+    <t>lõunapoolus</t>
+  </si>
+  <si>
+    <t>south pole</t>
+  </si>
+  <si>
+    <t>jäämägi</t>
+  </si>
+  <si>
+    <t>iceberg</t>
+  </si>
+  <si>
+    <t>jää</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>nire</t>
+  </si>
+  <si>
+    <t>trickle</t>
+  </si>
+  <si>
+    <t>lill</t>
+  </si>
+  <si>
+    <t>flower</t>
+  </si>
+  <si>
+    <t>leht</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>kroonleht</t>
+  </si>
+  <si>
+    <t>petal</t>
+  </si>
+  <si>
+    <t>oks</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>okas</t>
+  </si>
+  <si>
+    <t>puutüvi</t>
+  </si>
+  <si>
+    <t>trunk</t>
+  </si>
+  <si>
+    <t>juur</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>muld</t>
+  </si>
+  <si>
+    <t>soil</t>
+  </si>
+  <si>
+    <t>needle / thorn</t>
+  </si>
+  <si>
+    <t>sild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge </t>
+  </si>
+  <si>
+    <t>tänav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">street </t>
+  </si>
+  <si>
+    <t>väljak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">square </t>
+  </si>
+  <si>
+    <t>piir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">border </t>
+  </si>
+  <si>
+    <t>org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valley </t>
+  </si>
+  <si>
+    <t>tasandik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plain </t>
+  </si>
+  <si>
+    <t>rannik</t>
+  </si>
+  <si>
+    <t>coast</t>
+  </si>
+  <si>
+    <t>laht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bay </t>
+  </si>
+  <si>
+    <t>juga</t>
+  </si>
+  <si>
+    <t>maavärin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earthquake </t>
+  </si>
+  <si>
+    <t>maastik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">landscape </t>
+  </si>
+  <si>
+    <t>küngas</t>
+  </si>
+  <si>
+    <t>hill</t>
+  </si>
+  <si>
+    <t>swamp</t>
+  </si>
+  <si>
+    <t>beach</t>
+  </si>
+  <si>
+    <t>maa</t>
+  </si>
+  <si>
+    <t>maailmajagu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">continent </t>
+  </si>
+  <si>
+    <t>riik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">country </t>
+  </si>
+  <si>
+    <t>sisemaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inland </t>
+  </si>
+  <si>
+    <t>earth / land</t>
+  </si>
+  <si>
+    <t>põhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north </t>
+  </si>
+  <si>
+    <t>lõuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south </t>
+  </si>
+  <si>
+    <t>ida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">east </t>
+  </si>
+  <si>
+    <t>lääs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">west </t>
+  </si>
+  <si>
+    <t>kirre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">northeast </t>
+  </si>
+  <si>
+    <t>kagu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">southeast </t>
+  </si>
+  <si>
+    <t>loe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">northwest </t>
+  </si>
+  <si>
+    <t>edel</t>
+  </si>
+  <si>
+    <t>southwest</t>
+  </si>
+  <si>
+    <t>täht</t>
+  </si>
+  <si>
+    <t>star</t>
+  </si>
+  <si>
+    <t>tulnukas</t>
+  </si>
+  <si>
+    <t>alien</t>
+  </si>
+  <si>
+    <t>ükssarvik</t>
+  </si>
+  <si>
+    <t>unicorn</t>
+  </si>
+  <si>
+    <t>lohe</t>
+  </si>
+  <si>
+    <t>dragon</t>
+  </si>
+  <si>
+    <t>kummitus</t>
+  </si>
+  <si>
+    <t>ghost</t>
+  </si>
+  <si>
+    <t>rüütel</t>
+  </si>
+  <si>
+    <t>knight</t>
+  </si>
+  <si>
+    <t>nõid</t>
+  </si>
+  <si>
+    <t>witch</t>
+  </si>
+  <si>
+    <t>võlur</t>
+  </si>
+  <si>
+    <t>magician</t>
+  </si>
+  <si>
+    <t>hiiglane</t>
+  </si>
+  <si>
+    <t>giant</t>
+  </si>
+  <si>
+    <t>koletis</t>
+  </si>
+  <si>
+    <t>monster</t>
+  </si>
+  <si>
+    <t>merineitsi</t>
+  </si>
+  <si>
+    <t>mermaid</t>
+  </si>
+  <si>
+    <t>haldjas</t>
+  </si>
+  <si>
+    <t>fairy</t>
+  </si>
+  <si>
+    <t>mõõk</t>
+  </si>
+  <si>
+    <t>sword</t>
+  </si>
+  <si>
+    <t>päkapikk</t>
+  </si>
+  <si>
+    <t>dwarf / gnome</t>
+  </si>
+  <si>
+    <t>libahunt</t>
+  </si>
+  <si>
+    <t>werewolf</t>
+  </si>
+  <si>
+    <t>kangelane</t>
+  </si>
+  <si>
+    <t>hero</t>
+  </si>
+  <si>
+    <t>kurikael</t>
+  </si>
+  <si>
+    <t>villain</t>
+  </si>
+  <si>
+    <t>aare</t>
+  </si>
+  <si>
+    <t>treasure</t>
+  </si>
+  <si>
+    <t>kuningas</t>
+  </si>
+  <si>
+    <t>kuninganna</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>queen</t>
+  </si>
+  <si>
+    <t>prints</t>
+  </si>
+  <si>
+    <t>printsess</t>
+  </si>
+  <si>
+    <t>prince</t>
+  </si>
+  <si>
+    <t>princess</t>
+  </si>
+  <si>
+    <t>torn</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>kilp</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>loits</t>
+  </si>
+  <si>
+    <t>spell</t>
+  </si>
+  <si>
+    <t>needus</t>
+  </si>
+  <si>
+    <t>curse</t>
+  </si>
+  <si>
+    <t>aardekirst</t>
+  </si>
+  <si>
+    <t>treasure chest</t>
+  </si>
+  <si>
+    <t>vaim</t>
+  </si>
+  <si>
+    <t>spirit</t>
+  </si>
+  <si>
+    <t>saatus</t>
+  </si>
+  <si>
+    <t>fate</t>
+  </si>
+  <si>
+    <t>ime</t>
+  </si>
+  <si>
+    <t>miracle</t>
+  </si>
+  <si>
+    <t>saladus</t>
+  </si>
+  <si>
+    <t>secret</t>
+  </si>
+  <si>
+    <t>seiklus</t>
+  </si>
+  <si>
+    <t>teekond</t>
+  </si>
+  <si>
+    <t>lahing</t>
+  </si>
+  <si>
+    <t>pulm</t>
+  </si>
+  <si>
+    <t>suudlus</t>
+  </si>
+  <si>
+    <t>adventure</t>
+  </si>
+  <si>
+    <t>journey</t>
+  </si>
+  <si>
+    <t>battle</t>
+  </si>
+  <si>
+    <t>wedding</t>
+  </si>
+  <si>
+    <t>kiss</t>
+  </si>
+  <si>
+    <t>oda</t>
+  </si>
+  <si>
+    <t>spear</t>
+  </si>
+  <si>
+    <t>vibu</t>
+  </si>
+  <si>
+    <t>bow</t>
+  </si>
+  <si>
+    <t>nool</t>
+  </si>
+  <si>
+    <t>arrow</t>
+  </si>
+  <si>
+    <t>kirves</t>
+  </si>
+  <si>
+    <t>axe</t>
+  </si>
+  <si>
+    <t>pistoda</t>
+  </si>
+  <si>
+    <t>dagger</t>
+  </si>
+  <si>
+    <t>kahur</t>
+  </si>
+  <si>
+    <t>cannon</t>
+  </si>
+  <si>
+    <t>relv</t>
+  </si>
+  <si>
+    <t>weapon</t>
+  </si>
+  <si>
+    <t>kiiver</t>
+  </si>
+  <si>
+    <t>helmet</t>
+  </si>
+  <si>
+    <t>kuul</t>
+  </si>
+  <si>
+    <t>bullet</t>
+  </si>
+  <si>
+    <t>pomm</t>
+  </si>
+  <si>
+    <t>bomb</t>
+  </si>
+  <si>
+    <t>Fairytale &amp; Weapons</t>
+  </si>
+  <si>
+    <t>taste adjectives</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3598,8 +5677,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3609,12 +5701,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3630,18 +5716,127 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4050,7 +6245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C580"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -4164,7 +6359,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -4186,7 +6381,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -4208,7 +6403,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -4975,10 +7170,10 @@
         <v>135</v>
       </c>
       <c r="B84" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="C84" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -4986,10 +7181,10 @@
         <v>135</v>
       </c>
       <c r="B85" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="C85" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -6804,7 +8999,7 @@
         <v>437</v>
       </c>
       <c r="C250" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -6815,7 +9010,7 @@
         <v>438</v>
       </c>
       <c r="C251" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
@@ -6826,7 +9021,7 @@
         <v>439</v>
       </c>
       <c r="C252" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
@@ -6837,7 +9032,7 @@
         <v>440</v>
       </c>
       <c r="C253" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
@@ -6848,7 +9043,7 @@
         <v>441</v>
       </c>
       <c r="C254" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
@@ -6859,7 +9054,7 @@
         <v>442</v>
       </c>
       <c r="C255" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -6870,7 +9065,7 @@
         <v>443</v>
       </c>
       <c r="C256" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
@@ -6881,7 +9076,7 @@
         <v>444</v>
       </c>
       <c r="C257" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -7200,7 +9395,7 @@
         <v>468</v>
       </c>
       <c r="C286" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
@@ -7384,10 +9579,10 @@
         <v>482</v>
       </c>
       <c r="B303" t="s">
+        <v>958</v>
+      </c>
+      <c r="C303" t="s">
         <v>959</v>
-      </c>
-      <c r="C303" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
@@ -7604,10 +9799,10 @@
         <v>482</v>
       </c>
       <c r="B323" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C323" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
@@ -7692,10 +9887,10 @@
         <v>482</v>
       </c>
       <c r="B331" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="C331" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
@@ -7824,10 +10019,10 @@
         <v>482</v>
       </c>
       <c r="B343" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C343" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
@@ -8110,10 +10305,10 @@
         <v>482</v>
       </c>
       <c r="B369" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C369" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
@@ -8121,10 +10316,10 @@
         <v>482</v>
       </c>
       <c r="B370" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="C370" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
@@ -8132,10 +10327,10 @@
         <v>482</v>
       </c>
       <c r="B371" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C371" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
@@ -8143,10 +10338,10 @@
         <v>482</v>
       </c>
       <c r="B372" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C372" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
@@ -8154,10 +10349,10 @@
         <v>482</v>
       </c>
       <c r="B373" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C373" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
@@ -8165,10 +10360,10 @@
         <v>482</v>
       </c>
       <c r="B374" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C374" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
@@ -8209,10 +10404,10 @@
         <v>482</v>
       </c>
       <c r="B378" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C378" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
@@ -8220,10 +10415,10 @@
         <v>482</v>
       </c>
       <c r="B379" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="C379" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
@@ -8231,10 +10426,10 @@
         <v>482</v>
       </c>
       <c r="B380" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C380" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
@@ -8242,10 +10437,10 @@
         <v>482</v>
       </c>
       <c r="B381" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="C381" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
@@ -8253,10 +10448,10 @@
         <v>482</v>
       </c>
       <c r="B382" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="C382" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
@@ -8264,10 +10459,10 @@
         <v>482</v>
       </c>
       <c r="B383" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C383" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
@@ -8275,10 +10470,10 @@
         <v>482</v>
       </c>
       <c r="B384" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C384" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
@@ -8286,10 +10481,10 @@
         <v>482</v>
       </c>
       <c r="B385" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="C385" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
@@ -8297,10 +10492,10 @@
         <v>482</v>
       </c>
       <c r="B386" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="C386" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
@@ -8308,10 +10503,10 @@
         <v>482</v>
       </c>
       <c r="B387" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="C387" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
@@ -8319,10 +10514,10 @@
         <v>482</v>
       </c>
       <c r="B388" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C388" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
@@ -8330,10 +10525,10 @@
         <v>482</v>
       </c>
       <c r="B389" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C389" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
@@ -8341,10 +10536,10 @@
         <v>482</v>
       </c>
       <c r="B390" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="C390" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
@@ -8352,10 +10547,10 @@
         <v>482</v>
       </c>
       <c r="B391" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C391" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
@@ -8363,10 +10558,10 @@
         <v>482</v>
       </c>
       <c r="B392" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="C392" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
@@ -8374,10 +10569,10 @@
         <v>482</v>
       </c>
       <c r="B393" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="C393" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
@@ -8385,10 +10580,10 @@
         <v>482</v>
       </c>
       <c r="B394" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C394" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
@@ -8396,10 +10591,10 @@
         <v>482</v>
       </c>
       <c r="B395" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C395" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
@@ -8407,10 +10602,10 @@
         <v>482</v>
       </c>
       <c r="B396" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="C396" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
@@ -8418,10 +10613,10 @@
         <v>482</v>
       </c>
       <c r="B397" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="C397" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
@@ -8429,10 +10624,10 @@
         <v>482</v>
       </c>
       <c r="B398" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C398" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
@@ -8440,10 +10635,10 @@
         <v>482</v>
       </c>
       <c r="B399" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="C399" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
@@ -8451,10 +10646,10 @@
         <v>482</v>
       </c>
       <c r="B400" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C400" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
@@ -8462,10 +10657,10 @@
         <v>482</v>
       </c>
       <c r="B401" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C401" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
@@ -8473,10 +10668,10 @@
         <v>482</v>
       </c>
       <c r="B402" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="C402" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
@@ -8484,10 +10679,10 @@
         <v>482</v>
       </c>
       <c r="B403" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C403" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
@@ -8495,10 +10690,10 @@
         <v>482</v>
       </c>
       <c r="B404" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C404" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
@@ -8506,10 +10701,10 @@
         <v>482</v>
       </c>
       <c r="B405" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C405" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
@@ -8517,10 +10712,10 @@
         <v>482</v>
       </c>
       <c r="B406" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="C406" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
@@ -8531,7 +10726,7 @@
         <v>723</v>
       </c>
       <c r="C407" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
@@ -8641,7 +10836,7 @@
         <v>733</v>
       </c>
       <c r="C417" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
@@ -8674,7 +10869,7 @@
         <v>736</v>
       </c>
       <c r="C420" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
@@ -8740,7 +10935,7 @@
         <v>742</v>
       </c>
       <c r="C426" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
@@ -8817,7 +11012,7 @@
         <v>749</v>
       </c>
       <c r="C433" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
@@ -8836,7 +11031,7 @@
         <v>808</v>
       </c>
       <c r="B435" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="C435" t="s">
         <v>790</v>
@@ -9053,18 +11248,18 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B455" t="s">
         <v>813</v>
       </c>
       <c r="C455" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B456" t="s">
         <v>814</v>
@@ -9075,7 +11270,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B457" t="s">
         <v>815</v>
@@ -9086,7 +11281,7 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B458" t="s">
         <v>816</v>
@@ -9097,7 +11292,7 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B459" t="s">
         <v>817</v>
@@ -9108,7 +11303,7 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B460" t="s">
         <v>818</v>
@@ -9119,7 +11314,7 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B461" t="s">
         <v>819</v>
@@ -9130,18 +11325,18 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B462" t="s">
         <v>820</v>
       </c>
       <c r="C462" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B463" t="s">
         <v>821</v>
@@ -9152,7 +11347,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B464" t="s">
         <v>822</v>
@@ -9163,7 +11358,7 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B465" t="s">
         <v>823</v>
@@ -9174,7 +11369,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B466" t="s">
         <v>824</v>
@@ -9185,7 +11380,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B467" t="s">
         <v>825</v>
@@ -9196,7 +11391,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B468" t="s">
         <v>826</v>
@@ -9207,7 +11402,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B469" t="s">
         <v>827</v>
@@ -9218,18 +11413,18 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B470" t="s">
         <v>828</v>
       </c>
       <c r="C470" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B471" t="s">
         <v>829</v>
@@ -9240,7 +11435,7 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B472" t="s">
         <v>830</v>
@@ -9251,7 +11446,7 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B473" t="s">
         <v>831</v>
@@ -9262,7 +11457,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B474" t="s">
         <v>832</v>
@@ -9273,7 +11468,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B475" t="s">
         <v>833</v>
@@ -9284,7 +11479,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B476" t="s">
         <v>834</v>
@@ -9295,7 +11490,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B477" t="s">
         <v>835</v>
@@ -9306,7 +11501,7 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B478" t="s">
         <v>836</v>
@@ -9317,7 +11512,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B479" t="s">
         <v>837</v>
@@ -9328,590 +11523,590 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B480" t="s">
         <v>864</v>
       </c>
-      <c r="B480" t="s">
-        <v>865</v>
-      </c>
       <c r="C480" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B481" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C481" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B482" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C482" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B483" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C483" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B484" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C484" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B485" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C485" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B486" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C486" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B487" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C487" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B488" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C488" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B489" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C489" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B490" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C490" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B491" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C491" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B492" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C492" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B493" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C493" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B494" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C494" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B495" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C495" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B496" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C496" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B497" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C497" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B498" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C498" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B499" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C499" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B500" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C500" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B501" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C501" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B502" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C502" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B503" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C503" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B504" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C504" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B505" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C505" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B506" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C506" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B507" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C507" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B508" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C508" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B509" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C509" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B510" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C510" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B511" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C511" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B512" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C512" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B513" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C513" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B514" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C514" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B515" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C515" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B516" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C516" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B517" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C517" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B518" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C518" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B519" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C519" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B520" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C520" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B521" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C521" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B522" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C522" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B523" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C523" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A524" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B524" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C524" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B525" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C525" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A526" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B526" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C526" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B527" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C527" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A528" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B528" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C528" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B529" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C529" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A530" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B530" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C530" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B531" t="s">
         <v>965</v>
       </c>
       <c r="C531" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A532" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B532" t="s">
         <v>966</v>
       </c>
       <c r="C532" t="s">
-        <v>1020</v>
+        <v>988</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B533" t="s">
         <v>967</v>
@@ -9922,7 +12117,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A534" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B534" t="s">
         <v>968</v>
@@ -9933,7 +12128,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B535" t="s">
         <v>969</v>
@@ -9944,7 +12139,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B536" t="s">
         <v>970</v>
@@ -9955,7 +12150,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B537" t="s">
         <v>971</v>
@@ -9966,29 +12161,29 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B538" t="s">
         <v>972</v>
       </c>
       <c r="C538" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B539" t="s">
         <v>973</v>
       </c>
       <c r="C539" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A540" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B540" t="s">
         <v>974</v>
@@ -9999,29 +12194,29 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B541" t="s">
         <v>975</v>
       </c>
       <c r="C541" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A542" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B542" t="s">
         <v>976</v>
       </c>
       <c r="C542" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B543" t="s">
         <v>977</v>
@@ -10032,7 +12227,7 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A544" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B544" t="s">
         <v>978</v>
@@ -10043,7 +12238,7 @@
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B545" t="s">
         <v>979</v>
@@ -10054,7 +12249,7 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A546" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B546" t="s">
         <v>980</v>
@@ -10065,51 +12260,51 @@
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B547" t="s">
         <v>981</v>
       </c>
       <c r="C547" t="s">
-        <v>1001</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A548" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B548" t="s">
         <v>982</v>
       </c>
       <c r="C548" t="s">
-        <v>1027</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B549" t="s">
-        <v>983</v>
+        <v>1153</v>
       </c>
       <c r="C549" t="s">
-        <v>1002</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A550" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B550" t="s">
-        <v>1157</v>
+        <v>983</v>
       </c>
       <c r="C550" t="s">
-        <v>1159</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B551" t="s">
         <v>984</v>
@@ -10120,18 +12315,18 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A552" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B552" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="C552" t="s">
-        <v>1004</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B553" t="s">
         <v>1028</v>
@@ -10142,320 +12337,4289 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A554" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B554" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C554" t="s">
         <v>1031</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B555" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C555" t="s">
         <v>1033</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A556" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B556" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C556" t="s">
         <v>1035</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B557" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C557" t="s">
         <v>1037</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A558" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B558" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C558" t="s">
         <v>1039</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B559" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C559" t="s">
         <v>1041</v>
-      </c>
-      <c r="C559" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A560" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B560" t="s">
-        <v>1043</v>
+        <v>1158</v>
       </c>
       <c r="C560" t="s">
-        <v>1044</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B561" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C561" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A562" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B562" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="C562" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B563" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C563" t="s">
         <v>1164</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A564" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B564" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C564" t="s">
         <v>1165</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B565" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C565" t="s">
         <v>1166</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A566" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B566" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C566" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A567" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A568" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C568" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A569" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C569" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A570" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C570" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A571" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C571" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A572" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C572" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A573" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B573" t="s">
+        <v>964</v>
+      </c>
+      <c r="C573" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A574" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C574" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A575" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C575" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A576" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C576" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A577" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C577" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A578" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C578" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A579" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C579" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A580" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C580" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A581" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C581" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A582" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C582" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A583" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C583" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A584" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C584" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A585" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C585" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A586" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C586" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A587" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C587" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A588" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C588" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A589" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C589" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A590" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C590" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A591" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C591" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A592" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C592" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A593" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C593" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C594" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C595" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A596" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C596" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A597" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C597" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A598" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C598" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A599" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C599" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A600" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C600" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A601" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C601" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A602" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C602" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A603" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C603" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A604" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C604" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A605" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C605" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A606" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C606" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A607" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C607" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A608" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C608" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A609" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A610" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C610" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A611" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C611" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A612" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C612" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A613" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C613" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A614" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C614" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A615" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C615" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A616" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B616" s="3" t="s">
         <v>1170</v>
       </c>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A567" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A568" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B568" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A569" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B569" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A570" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B570" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A571" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B571" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A572" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B572" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A573" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B573" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A574" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B574" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A575" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B575" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C575" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A576" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B576" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A577" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B577" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C577" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A578" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B578" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C578" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A579" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B579" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A580" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B580" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1068</v>
+      <c r="C616" s="3" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A617" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A618" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A619" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A620" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A621" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A622" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A623" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A624" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A625" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A626" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A627" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A628" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A629" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A630" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A631" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A632" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A633" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A634" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A635" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A636" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A638" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A641" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A642" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A643" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A644" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A645" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A646" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A647" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A648" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A649" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A654" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A655" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A656" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A657" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A658" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A659" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A660" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A661" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A662" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A663" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A664" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A665" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A666" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A667" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A668" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A669" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A670" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A671" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A672" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A673" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A674" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A675" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A676" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A677" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A678" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A679" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A680" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A681" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A682" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B682" t="s">
+        <v>672</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A683" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A684" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C684" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A685" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A686" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A687" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A688" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A689" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A690" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A691" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A692" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A693" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A694" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A695" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C695" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A696" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C696" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A697" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C697" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A698" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C698" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A699" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C699" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A700" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C700" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A701" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C701" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A702" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C702" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A703" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C703" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A704" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C704" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A705" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C705" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A706" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C706" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A707" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A708" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A709" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B709" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A710" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A711" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B711" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A712" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A713" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B713" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A714" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A715" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B715" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A716" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B716" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A717" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A718" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A719" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B719" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A720" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B720" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A721" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B721" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A722" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B722" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A723" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B723" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A724" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A725" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A726" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B726" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A727" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B727" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A728" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A729" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B729" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A730" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B730" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A731" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B731" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A732" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B732" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C732" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A733" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B733" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C733" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A734" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B734" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C734" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A735" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B735" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C735" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A736" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B736" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C736" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A737" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B737" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C737" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A738" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B738" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A739" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B739" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A740" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B740" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A741" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B741" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A742" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B742" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A743" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B743" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A744" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B744" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A745" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B745" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A746" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B746" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A747" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B747" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A748" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B748" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A749" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B749" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A750" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B750" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C750" s="3" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A751" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B751" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C751" s="3" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A752" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B752" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C752" s="3" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A753" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B753" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C753" s="3" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A754" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B754" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C754" s="3" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A755" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B755" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C755" s="3" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A756" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B756" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C756" s="3" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A757" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B757" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C757" s="3" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A758" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B758" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A759" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B759" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C759" s="3" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A760" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B760" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C760" s="3" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A761" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B761" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C761" s="3" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A762" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B762" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C762" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A763" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B763" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C763" s="3" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A764" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B764" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C764" s="3" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A765" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B765" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C765" s="3" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A766" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B766" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A767" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B767" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A768" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B768" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A769" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B769" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C769" s="3" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A770" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B770" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A771" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B771" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A772" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B772" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C772" s="3" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A773" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B773" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C773" s="3" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A774" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B774" s="5" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C774" s="5" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A775" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B775" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C775" s="3" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A776" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B776" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C776" s="3" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A777" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B777" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C777" s="3" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A778" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B778" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C778" s="3" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A779" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B779" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C779" s="3" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A780" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B780" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C780" s="3" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A781" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B781" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C781" s="3" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A782" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B782" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C782" s="3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A783" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B783" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C783" s="3" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A784" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B784" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C784" s="3" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A785" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B785" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C785" s="3" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A786" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B786" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C786" s="3" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A787" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B787" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C787" s="3" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A788" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B788" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C788" s="3" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A789" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B789" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C789" s="3" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A790" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B790" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C790" s="3" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A791" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B791" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C791" s="3" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A792" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B792" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C792" s="3" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A793" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B793" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C793" s="3" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A794" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B794" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C794" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A795" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B795" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C795" s="3" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A796" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B796" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C796" s="3" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A797" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B797" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C797" s="3" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A798" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B798" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C798" s="3" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A799" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B799" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C799" s="3" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A800" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B800" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C800" s="3" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A801" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B801" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C801" s="3" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A802" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B802" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C802" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A803" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B803" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C803" s="3" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A804" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B804" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C804" s="3" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A805" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B805" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C805" s="3" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A806" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B806" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C806" s="3" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A807" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B807" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C807" s="3" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A808" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B808" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C808" s="3" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A809" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B809" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C809" s="3" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A810" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B810" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C810" s="3" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A811" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B811" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C811" s="3" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A812" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B812" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C812" s="3" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A813" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B813" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C813" s="3" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A814" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B814" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C814" s="3" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A815" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B815" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C815" s="3" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A816" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B816" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C816" s="3" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A817" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B817" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C817" s="3" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A818" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B818" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C818" s="3" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A819" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B819" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C819" s="3" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A820" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B820" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C820" s="3" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A821" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B821" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C821" s="3" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A822" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B822" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C822" s="3" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A823" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B823" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C823" s="3" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A824" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B824" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C824" s="3" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A825" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B825" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C825" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A826" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C826" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A827" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B827" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C827" s="7" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A828" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B828" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C828" s="3" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A829" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B829" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C829" s="3" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A830" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B830" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C830" s="3" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A831" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B831" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C831" s="3" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A832" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C832" s="8" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A833" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B833" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C833" s="3" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A834" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B834" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C834" s="3" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A835" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B835" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C835" s="3" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A836" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B836" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C836" s="3" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A837" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B837" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C837" s="3" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A838" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B838" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C838" s="3" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A839" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B839" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C839" s="3" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A840" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B840" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C840" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A841" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B841" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C841" s="3" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A842" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B842" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C842" s="3" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A843" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B843" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C843" s="3" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A844" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B844" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C844" s="3" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A845" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B845" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C845" s="3" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A846" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C846" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A847" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B847" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C847" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A848" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C848" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A849" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B849" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C849" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A850" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B850" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C850" s="3" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A851" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B851" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C851" s="3" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A852" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B852" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C852" s="8" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A853" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B853" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C853" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A854" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B854" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C854" s="3" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A855" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B855" s="3" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C855" s="3" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A856" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B856" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C856" s="8" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A857" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B857" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C857" s="8" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A858" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B858" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C858" s="8" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A859" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B859" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C859" s="8" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A860" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B860" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C860" s="8" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A861" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B861" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C861" s="8" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A862" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B862" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C862" s="8" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A863" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B863" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C863" s="8" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A864" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B864" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C864" s="8" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A865" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B865" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C865" s="8" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A866" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B866" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C866" s="8" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A867" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B867" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C867" s="8" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A868" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B868" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C868" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A869" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B869" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C869" s="7" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A870" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B870" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C870" s="7" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A871" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B871" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C871" s="3" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A872" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C872" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A873" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C873" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A874" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B874" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C874" s="7" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A875" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C875" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A876" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C876" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A877" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C877" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A878" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C878" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A879" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C879" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A880" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C880" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A881" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C881" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A882" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C882" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A883" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C883" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A884" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C884" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A885" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C885" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A886" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C886" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A887" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C887" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A888" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C888" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A889" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C889" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A890" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C890" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A891" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B891" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C891" s="3" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A892" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B892" s="7" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C892" s="7" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A893" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B893" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C893" s="3" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A894" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B894" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C894" s="8" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A895" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B895" s="3" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C895" s="3" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A896" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C896" s="3" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A897" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B897" s="3" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C897" s="3" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A898" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B898" s="3" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C898" s="8" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A899" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B899" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C899" s="3" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A900" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B900" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C900" s="3" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A901" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B901" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C901" s="3" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A902" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B902" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C902" s="3" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A903" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B903" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C903" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A904" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B904" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C904" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A905" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B905" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C905" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A906" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A907" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C907" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A908" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A909" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A910" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A911" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A912" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B912" t="s">
+        <v>981</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A913" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B913" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A914" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B914" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A915" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B915" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C915" s="8" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A916" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B916" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A917" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A918" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C918" s="3" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A919" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A920" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C920" s="8" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A921" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B921" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C921" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A922" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C922" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A923" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C923" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A924" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C924" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A925" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C925" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A926" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B926" s="3" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A927" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B927" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A928" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B928" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A929" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B929" s="3" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A930" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B930" s="3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A931" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A932" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B932" s="3" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A933" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B933" s="3" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C933" s="3" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A934" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B934" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C934" s="3" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A935" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B935" s="3" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C935" s="3" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A936" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C936" s="3" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A937" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C937" s="3" t="s">
+        <v>1868</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B35:B53 B4:B5 B13">
-    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C89">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B676:B731 B1:B565 B567:B615 B825 B938:B1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B676:B731 B528:B565 B444:B526 B1:B379 B407:B442 B567:B615 B825 B938:B1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B676:B731 B528:B565 B444:B526 B276:B379 B407:B442 B185:B217 B219:B247 B251:B269 B271 B75:B182 B1:B73 B218:C218 C219 B567:B615 B825 B938:B1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813:B824 B776:B798 B732:B774">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B827 B868:B871 B874">
+    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B856:B867 B852">
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B832">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B875:B876 B873">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B880:B887">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888:C890 B833:C872 B874:C874 B877:C878 B827:C831">
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888:B890 B846:B849 B840 B872 B877:B878">
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B528:B1048576 B444:B526 B1:B379 B407:B442">
-    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B528:B1048576 B444:B526 B276:B379 B407:B442 B185:B217 B219:B247 B251:B269 B271 B75:B182 B1:B73 B218:C218 C219">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  <conditionalFormatting sqref="B899:C903 B892:C893 B895:C895 B912:C913 C906 C908:C911 B897:C897 C896 C914:C920">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10464,7 +16628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -10545,7 +16709,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -10553,66 +16717,104 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>1005</v>
+        <v>1468</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>1069</v>
+      <c r="A12" s="2" t="s">
+        <v>1263</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B13" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B14" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+    </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>1174</v>
+      <c r="A16" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B16" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>1175</v>
+      <c r="A20" s="2" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>1160</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>1161</v>
-      </c>
+      <c r="A25" s="4"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>1173</v>
-      </c>
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>1177</v>
-      </c>
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>